--- a/evaluation/train-test-splits/split_statistics.xlsx
+++ b/evaluation/train-test-splits/split_statistics.xlsx
@@ -476,31 +476,35 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>217</v>
+        <v>150</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
-      </c>
-      <c r="E2" t="n">
-        <v>413</v>
-      </c>
-      <c r="F2" t="n">
-        <v>411</v>
+        <v>2.778</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>379.396</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1588.951</v>
+        <v>3586.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1209.555</v>
+        <v>3581.6</v>
       </c>
       <c r="J2" t="n">
-        <v>361.7209999999997</v>
+        <v>1311.45</v>
       </c>
     </row>
     <row r="3">
@@ -510,31 +514,35 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E3" t="n">
-        <v>413</v>
-      </c>
-      <c r="F3" t="n">
-        <v>411</v>
+        <v>3.417</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
       <c r="G3" t="n">
-        <v>379.396</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>1434.486</v>
+        <v>2717.85</v>
       </c>
       <c r="I3" t="n">
-        <v>1055.09</v>
+        <v>2712.85</v>
       </c>
       <c r="J3" t="n">
-        <v>294.3919999999995</v>
+        <v>973.0000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -544,31 +552,35 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>412</v>
-      </c>
-      <c r="F4" t="n">
-        <v>408</v>
+        <v>1.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>1434.519</v>
+        <v>2737.15</v>
       </c>
       <c r="H4" t="n">
-        <v>1588.951</v>
+        <v>3586.6</v>
       </c>
       <c r="I4" t="n">
-        <v>154.432</v>
+        <v>849.4499999999998</v>
       </c>
       <c r="J4" t="n">
-        <v>67.32900000000018</v>
+        <v>338.4500000000003</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,23 +640,25 @@
           <t>all</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>402</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3660000000001</v>
+        <v>378.500000000002</v>
       </c>
       <c r="E2" t="n">
-        <v>7.18300000000005</v>
+        <v>9.462500000000052</v>
       </c>
       <c r="F2" t="n">
-        <v>3.566000000000031</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>10.80000000000007</v>
+        <v>62.64999999999998</v>
       </c>
     </row>
     <row r="3">
@@ -653,23 +667,25 @@
           <t>all</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>404</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>22.20100000000042</v>
+        <v>583.5999999999987</v>
       </c>
       <c r="E3" t="n">
-        <v>1.850083333333368</v>
+        <v>11.67199999999997</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8000000000001819</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.299999999999955</v>
+        <v>95.84999999999991</v>
       </c>
     </row>
     <row r="4">
@@ -678,23 +694,25 @@
           <t>all</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>405</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>39.99700000000018</v>
+        <v>61.35000000000082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.754660377358494</v>
+        <v>3.408333333333379</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2659999999999627</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.133000000000038</v>
+        <v>29.90000000000009</v>
       </c>
     </row>
     <row r="5">
@@ -703,598 +721,241 @@
           <t>all</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>406</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>21.43299999999954</v>
+        <v>287.9999999999987</v>
       </c>
       <c r="E5" t="n">
-        <v>1.530928571428538</v>
+        <v>6.857142857142827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5999999999999091</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.867000000000019</v>
+        <v>120.9499999999998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>407</v>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>20.73099999999954</v>
+        <v>313.9500000000014</v>
       </c>
       <c r="E6" t="n">
-        <v>2.073099999999954</v>
+        <v>9.810937500000044</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5329999999999018</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.932999999999993</v>
+        <v>62.64999999999998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>408</v>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D7" t="n">
-        <v>6.5</v>
+        <v>484.6999999999995</v>
       </c>
       <c r="E7" t="n">
-        <v>3.25</v>
+        <v>11.82195121951218</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7000000000000455</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5.799999999999955</v>
+        <v>95.84999999999991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>409</v>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10.53200000000015</v>
+        <v>24.95000000000027</v>
       </c>
       <c r="E8" t="n">
-        <v>1.50457142857145</v>
+        <v>2.079166666666689</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5660000000000309</v>
+        <v>0.0500000000001819</v>
       </c>
       <c r="G8" t="n">
-        <v>2.700000000000045</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>410</v>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83300000000008</v>
+        <v>149.3999999999988</v>
       </c>
       <c r="E9" t="n">
-        <v>35.83300000000008</v>
+        <v>4.268571428571396</v>
       </c>
       <c r="F9" t="n">
-        <v>35.83300000000008</v>
+        <v>0.05000000000001137</v>
       </c>
       <c r="G9" t="n">
-        <v>35.83300000000008</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>411</v>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>2.234000000000151</v>
+        <v>64.55000000000064</v>
       </c>
       <c r="E10" t="n">
-        <v>2.234000000000151</v>
+        <v>8.06875000000008</v>
       </c>
       <c r="F10" t="n">
-        <v>2.234000000000151</v>
+        <v>1.200000000000273</v>
       </c>
       <c r="G10" t="n">
-        <v>2.234000000000151</v>
+        <v>26.40000000000009</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>412</v>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>31.99599999999998</v>
+        <v>98.89999999999918</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6955652173913039</v>
+        <v>10.9888888888888</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1999999999998181</v>
+        <v>1.349999999999909</v>
       </c>
       <c r="G11" t="n">
-        <v>2.133999999999901</v>
+        <v>40.94999999999982</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>413</v>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>155.8979999999996</v>
+        <v>36.40000000000055</v>
       </c>
       <c r="E12" t="n">
-        <v>2.25939130434782</v>
+        <v>6.066666666666758</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3669999999999618</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>14.06600000000003</v>
+        <v>29.90000000000009</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>402</v>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3660000000001</v>
+        <v>138.5999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.18300000000005</v>
+        <v>19.79999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>3.566000000000031</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>10.80000000000007</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>404</v>
-      </c>
-      <c r="C14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.13300000000044</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.590428571428634</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8000000000001819</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3.199999999999989</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>405</v>
-      </c>
-      <c r="C15" t="n">
-        <v>40</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30.83200000000045</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.7708000000000113</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.2659999999999627</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.133000000000038</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>406</v>
-      </c>
-      <c r="C16" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16.10099999999943</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.610099999999943</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5999999999999091</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.867000000000019</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>407</v>
-      </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" t="n">
-        <v>20.73099999999954</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.073099999999954</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.5329999999999018</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.932999999999993</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>409</v>
-      </c>
-      <c r="C18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>10.53200000000015</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.50457142857145</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.5660000000000309</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.700000000000045</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>410</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>35.83300000000008</v>
-      </c>
-      <c r="E19" t="n">
-        <v>35.83300000000008</v>
-      </c>
-      <c r="F19" t="n">
-        <v>35.83300000000008</v>
-      </c>
-      <c r="G19" t="n">
-        <v>35.83300000000008</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>411</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.234000000000151</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2.234000000000151</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.234000000000151</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.234000000000151</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>412</v>
-      </c>
-      <c r="C21" t="n">
-        <v>33</v>
-      </c>
-      <c r="D21" t="n">
-        <v>22.99799999999993</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.6969090909090889</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.2330000000000609</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.133999999999901</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>413</v>
-      </c>
-      <c r="C22" t="n">
-        <v>62</v>
-      </c>
-      <c r="D22" t="n">
-        <v>129.6319999999993</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.090838709677408</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.3669999999999618</v>
-      </c>
-      <c r="G22" t="n">
-        <v>12.43399999999997</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>404</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>11.06799999999998</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.213599999999997</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9339999999999691</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4.299999999999955</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>405</v>
-      </c>
-      <c r="C24" t="n">
-        <v>13</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9.164999999999736</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.7049999999999798</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.4329999999999927</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.100000000000136</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>406</v>
-      </c>
-      <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>5.332000000000107</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.333000000000027</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.7330000000001746</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.066000000000031</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>408</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.7000000000000455</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5.799999999999955</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>412</v>
-      </c>
-      <c r="C27" t="n">
-        <v>13</v>
-      </c>
-      <c r="D27" t="n">
-        <v>8.998000000000047</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.6921538461538498</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.1999999999998181</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.932999999999993</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>413</v>
-      </c>
-      <c r="C28" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" t="n">
-        <v>26.2660000000003</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.752285714285758</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5660000000000309</v>
-      </c>
-      <c r="G28" t="n">
-        <v>14.06600000000003</v>
+        <v>120.9499999999998</v>
       </c>
     </row>
   </sheetData>
